--- a/Tests/g17_setup2_with_3ed_sim_outputs.xlsx
+++ b/Tests/g17_setup2_with_3ed_sim_outputs.xlsx
@@ -1,58 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5440292_ad_unsw_edu_au/Documents/MyPhD-Workspace/Codes/LoRaMeshSimulator-V3/Tests/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F44E60175C7A885FED5B449649FDB679254D870F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4011390A-2605-4882-95B0-A25B3F788FE0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
-  <si>
-    <t>---&gt; DER:</t>
-  </si>
-  <si>
-    <t>---&gt; Avg Latency:</t>
-  </si>
-  <si>
-    <t>---&gt; Min Latency:</t>
-  </si>
-  <si>
-    <t>---&gt; Max Latency:</t>
-  </si>
-  <si>
-    <t>xxxxxx</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,268 +407,511 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="20.88671875" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col width="20.88671875" customWidth="1" min="7" max="7"/>
+    <col width="20.77734375" customWidth="1" min="8" max="8"/>
+    <col width="13.88671875" customWidth="1" min="9" max="9"/>
+    <col width="15.5546875" customWidth="1" min="10" max="10"/>
+    <col width="13.88671875" customWidth="1" min="11" max="11"/>
+    <col width="16.6640625" customWidth="1" min="12" max="12"/>
+    <col width="12.5546875" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1">
+    <row r="1">
+      <c r="A1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1" t="n">
         <v>9</v>
       </c>
-      <c r="C1">
+      <c r="C1" t="n">
         <v>3</v>
       </c>
-      <c r="D1">
+      <c r="D1" t="n">
         <v>10000</v>
       </c>
-      <c r="E1">
+      <c r="E1" t="n">
         <v>1000</v>
       </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1">
-        <v>0.89100000000000001</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1">
-        <v>5761.3778576804907</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1">
-        <v>36.19686490483582</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I1" t="n">
+        <v>15449.33101800137</v>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K1" t="n">
+        <v>589.9914679271897</v>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M1" t="n">
+        <v>54380.61392646466</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="M1">
-        <v>28890.41058220901</v>
+      <c r="D2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>9619.572944485211</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>540.1778128070291</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>35882.4626155369</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>9</v>
       </c>
-      <c r="C2">
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>20000</v>
-      </c>
-      <c r="E2">
+      <c r="D3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E3" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4776.1775431384003</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>41.841266728937633</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>6041.43259758518</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>548.3101659463719</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>24654.49451641153</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="M2">
-        <v>30915.645740807991</v>
+      <c r="D4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5784.10777684843</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>433.0093503836542</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>31165.46698072879</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>30000</v>
-      </c>
-      <c r="E3">
+      <c r="D5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E5" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0.96</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3648.0628312351059</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>38.33399545866996</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5260.994562670564</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>533.3177676913328</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>25898.26370682986</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
         <v>3</v>
       </c>
-      <c r="M3">
-        <v>22143.150371301919</v>
+      <c r="D6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5035.964783250047</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>460.6752079515718</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>20547.10742796818</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>40000</v>
-      </c>
-      <c r="E4">
+      <c r="D7" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E7" t="n">
         <v>1000</v>
       </c>
-      <c r="F4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0.96</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3385.5518631523892</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>47.621098129078753</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3429.703876126835</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>794.6956225633621</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>12183.70164638013</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="M4">
-        <v>25502.681257447461</v>
+      <c r="D8" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3637.726114442251</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>529.3825454860926</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>15609.92390206456</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="D5">
-        <v>50000</v>
-      </c>
-      <c r="E5">
+      <c r="D9" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E9" t="n">
         <v>1000</v>
       </c>
-      <c r="F5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0.96899999999999997</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3594.0540940881492</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>33.178173142718151</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3534.528489312972</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>512.0098648071289</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>19242.45125380158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="M5">
-        <v>19403.960452137511</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>60000</v>
-      </c>
-      <c r="E6">
+      <c r="D10" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E10" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.96699999999999997</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3407.788168197565</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>32.624004849232733</v>
-      </c>
-      <c r="L6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>30031.17450740188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3218.471185726898</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>737.4633719418198</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9739.032341599464</v>
       </c>
     </row>
   </sheetData>
